--- a/data/02_output/results_scientific_baseline.xlsx
+++ b/data/02_output/results_scientific_baseline.xlsx
@@ -56,7 +56,7 @@
     <t>data/01_input/250922_CS1_Wheat_Straw.xlsx</t>
   </si>
   <si>
-    <t>2025-09-22 16:16:00</t>
+    <t>2025-09-22 16:25:11</t>
   </si>
   <si>
     <t>2025 - 2050</t>

--- a/data/02_output/results_scientific_baseline.xlsx
+++ b/data/02_output/results_scientific_baseline.xlsx
@@ -56,7 +56,7 @@
     <t>data/01_input/250922_CS1_Wheat_Straw.xlsx</t>
   </si>
   <si>
-    <t>2025-09-22 16:25:11</t>
+    <t>2025-09-22 16:44:07</t>
   </si>
   <si>
     <t>2025 - 2050</t>

--- a/data/02_output/results_scientific_baseline.xlsx
+++ b/data/02_output/results_scientific_baseline.xlsx
@@ -56,7 +56,7 @@
     <t>data/01_input/250922_CS1_Wheat_Straw.xlsx</t>
   </si>
   <si>
-    <t>2025-09-22 16:44:07</t>
+    <t>2025-09-22 18:15:34</t>
   </si>
   <si>
     <t>2025 - 2050</t>

--- a/data/02_output/results_scientific_baseline.xlsx
+++ b/data/02_output/results_scientific_baseline.xlsx
@@ -56,7 +56,7 @@
     <t>data/01_input/250922_CS1_Wheat_Straw.xlsx</t>
   </si>
   <si>
-    <t>2025-09-22 18:15:34</t>
+    <t>2025-09-24 15:16:14</t>
   </si>
   <si>
     <t>2025 - 2050</t>
